--- a/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0008.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/skill_description/lang_multi_text/lang_multi_text__skill_description__part_0008.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Thực ra, ta vừa được báo là quản lý giao chỉ tiêu bán hàng cho ta đã bị cách chức rồi.</t>
+          <t>Thực ra, tao vừa được báo là quản lý giao chỉ tiêu bán hàng cho tao đã bị cách chức rồi.</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>I'm sorry... Chỉ tiêu doanh số vô lý không thể là cái cớ cho những bài báo tồi tệ của chúng ta.</t>
+          <t>Xin lỗi... Chỉ tiêu doanh số vô lý không thể là cái cớ cho những bài báo tồi tệ của chúng ta.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Mô hình trưng bày Resonance Nexus à?</t>
+          <t>Mô hình Trạm Cộng Hưởng mẫu?</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Sao cậu đoán được thế? Chính xác! Resonance Nexus và các Thiết bị đầu cuối ở Jinzhou mang đậm phong cách thiết kế độc đáo của Huanglong.</t>
+          <t>Sao cậu đoán được thế? Chính xác! Mạng Lưới Cộng Hưởng và các Thiết bị đầu cuối ở Jinzhou mang đậm phong cách thiết kế độc đáo của Huanglong.</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Hay mình đi xem Nexus Resonance đi, {PlayerName}?</t>
+          <t>Hay mình đi xem Nexus Cộng Hưởng đi, {PlayerName}?</t>
         </is>
       </c>
     </row>
@@ -1683,7 +1683,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Mấy ông Tư Vấn bảo bài Kiểm Tra Rabelle của ta cho thấy ta đã đánh thức được Forte. Nhưng ở làng, ta chẳng thấy mình có gì đặc biệt cả.</t>
+          <t>Mấy ông Tư Vấn bảo bài Kiểm Tra Rabelle của tao cho thấy tao đã đánh thức được Forte. Nhưng ở làng, tao chẳng thấy mình có gì đặc biệt cả.</t>
         </is>
       </c>
     </row>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Hừm, một cơ chế vận hành bằng Resonance, kích hoạt bởi các ký hiệu khắc. Vậy đây là cách người Septimont cổ xưa thanh tẩy tàn tích của Dark Tide sao?</t>
+          <t>Hừm, một cơ chế vận hành bằng Cộng Hưởng, kích hoạt bởi các ký hiệu khắc. Vậy đây là cách người Septimont cổ xưa thanh tẩy tàn tích của Dark Tide sao?</t>
         </is>
       </c>
     </row>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Nghệ thuật không phải sở trường của tôi.</t>
+          <t>Nghệ thuật không phải sở trường của tao đâu.</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Kẻ ngốc hóa kẻ thù</t>
+          <t>Kẻ ngu sẽ thành kẻ thù</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3775,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Đến Night Tưởng Niệm mà không đeo mặt nạ, cậu sẽ thành miếng mồi ngon cho những linh hồn lạc lối đấy!</t>
+          <t>Đến Đêm Tưởng Niệm mà không đeo mặt nạ, cậu sẽ thành miếng mồi ngon cho những linh hồn lạc lối đấy!</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3906,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Sau khi đọc tin nhắn kỳ lạ mà cậu nhận được, Cantarella giải thích rằng Night Tưởng Niệm xoay quanh chủ đề liên quan đến ma quỷ. Chủ đề tối nay tình cờ lại là "cô gái ma".
+          <t>Sau khi đọc tin nhắn kỳ lạ mà cậu nhận được, Cantarella giải thích rằng Đêm Tưởng Niệm xoay quanh chủ đề liên quan đến ma quỷ. Chủ đề tối nay tình cờ lại là "cô gái ma".
 Cô cảm nhận được tác động của nó lên cậu và mời cậu tham gia sự kiện, hứa rằng cậu sẽ hồi phục sau khi giải được những câu đố được chuẩn bị cho tối nay.</t>
         </is>
       </c>
@@ -5471,7 +5471,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Kẻ thù và đối thủ cũ à? Ta có thiếu đâu.</t>
+          <t>Kẻ thù và đối thủ cũ à? Tao có thiếu đâu.</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
       <c r="M80" t="inlineStr">
         <is>
           <t>Chào Nhà Thách Đấu {PlayerName}.
-Khoảnh khắc này, những vì sao đều thuộc về ngươi. Cảm ơn ngươi đã bước vào Colosseum Olymdos với lòng dũng cảm và kỹ năng, giữ cho ngọn lửa thi đấu mãi bừng sáng.
+Khoảnh khắc này, những vì sao đều thuộc về ngươi. Cảm ơn ngươi đã bước vào Đấu Trường Olymdos với lòng dũng cảm và kỹ năng, giữ cho ngọn lửa thi đấu mãi bừng sáng.
 Ta đã theo dõi ngươi từ khoảnh khắc ngươi đánh bại đối thủ đầu tiên. Chiến thuật, sự tập trung và đam mê của ngươi, cách ngươi trau chuốt từng bộ bài… tất cả đều gợi ta nhớ về tình yêu thuần khiết mà ta từng dành cho trò chơi này.
 Hãy chiến đấu hết mình, Nhà Thách Đấu! Trên chiến trường này, dốc hết sức lực chính là hình thức tôn trọng cao nhất mà một đấu thủ dành cho đối thủ của mình. Dù ngày mai ai sẽ là người chiến thắng, đấu trường này vẫn thuộc về cả hai ta, hai tâm hồn chiến đấu vì điều mình yêu quý.
 Mong bình minh mang đến cho chúng ta một bầu trời rộng lớn hơn ngày hôm qua.
@@ -6521,7 +6521,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Vậy khả năng Resonance của cậu là gì?</t>
+          <t>Vậy năng lực Cộng Hưởng của cậu là gì?</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Người ta bảo rằng Tỉnh Thức Resonance muộn thường phản ánh bản chất thật nhất của Resonator.</t>
+          <t>Người ta bảo rằng Tỉnh Thức Cộng Hưởng muộn thường phản ánh bản chất thật nhất của Resonator.</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6846,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Thôi, ta thoát được cái vụ kiểm tra sức khỏe đó rồi. Bác sĩ bảo tay ta hỏng rồi. Không bao giờ hồi phục hoàn toàn được nữa.</t>
+          <t>Thôi, tao thoát được cái vụ kiểm tra sức khỏe đó rồi. Bác sĩ bảo tay tao hỏng rồi. Không bao giờ hồi phục hoàn toàn được nữa.</t>
         </is>
       </c>
     </row>
@@ -6915,7 +6915,7 @@
       <c r="M99" t="inlineStr">
         <is>
           <t>Mục Tiêu Số 1: Kẻ Cắt Kéo Bí Ẩn
-Phần Thưởng: 2.000.000 Rice Dango
+Phần Thưởng: 2.000.000 Bánh Dango Gạo
 Khu Vực: Toàn Bộ Quận Honami
 Tình Trạng: Sắp Xảy Ra</t>
         </is>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Trong lúc truy đuổi Fenrico, cậu đã hiểu được mục tiêu thực sự của Phrolova: sức mạnh đồng hóa ẩn giấu bên trong Viên Threnodian's Gem.</t>
+          <t>Trong lúc truy đuổi Fenrico, cậu đã hiểu được mục tiêu thực sự của Phrolova: sức mạnh đồng hóa ẩn giấu bên trong Viên Ngọc Threnodian.</t>
         </is>
       </c>
     </row>
@@ -7762,7 +7762,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Anh là chuyên gia hàng đầu về thao túng nhận thức Resonance. Chúng tôi thực sự cần anh!</t>
+          <t>Anh là chuyên gia hàng đầu về thao túng nhận thức Cộng Hưởng. Chúng tôi thực sự cần anh!</t>
         </is>
       </c>
     </row>
@@ -7827,7 +7827,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Muốn trở thành Synchronist, cậu cần nhiều hơn là một Forte mạnh mẽ. Quan trọng hơn là phải hiểu được nó, để có thể đồng bộ và kích hoạt "Drive" của Exostrider.</t>
+          <t>Muốn trở thành Đồng Bộ Giả, cậu cần nhiều hơn là một Forte mạnh mẽ. Quan trọng hơn là phải hiểu được nó, để có thể đồng bộ và kích hoạt "Drive" của Exostrider.</t>
         </is>
       </c>
     </row>
@@ -9192,7 +9192,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Lần trước, có một học sinh thậm chí tập trung năng lượng Resonance lên trán rồi bắn bay một mảng trụ này! Trời ạ, đây là trụ CHỊU LỰC đấy!</t>
+          <t>Lần trước, có một học sinh thậm chí tập trung năng lượng Cộng Hưởng lên trán rồi bắn bay một mảng trụ này! Trời ạ, đây là trụ CHỊU LỰC đấy!</t>
         </is>
       </c>
     </row>
@@ -9322,7 +9322,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Area 51 hầu như chưa được khám phá, nhưng mức độ nguy hiểm lại cực cao. Có lẽ chúng ta chưa đủ khả năng để đối phó ở trình độ hiện tại...</t>
+          <t>Khu vực 51 hầu như chưa được khám phá, nhưng mức độ nguy hiểm lại cực cao. Có lẽ chúng ta chưa đủ khả năng để đối phó ở trình độ hiện tại...</t>
         </is>
       </c>
     </row>
@@ -9387,7 +9387,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Nhắc mới nhớ, hồi trước ở Học viện có một học sinh nhỉ? Ta nhớ các thông số Resonance của cô ấy gần như đạt đến mức Đồng Bộ Hoàn Hảo.</t>
+          <t>Nhắc mới nhớ, hồi trước ở Học viện có một học sinh nhỉ? Ta nhớ các thông số Cộng Hưởng của cô ấy gần như đạt đến mức Đồng Bộ Hoàn Hảo.</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Hơn nữa, nấu nướng và thưởng thức một bữa ăn nóng có thể giúp giảm bớt căng thẳng cho Synchronist...</t>
+          <t>Hơn nữa, nấu nướng và thưởng thức một bữa ăn nóng có thể giúp giảm bớt căng thẳng cho Đồng Bộ Giả...</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Ở Startorch Academy, ai cũng biết Void Storm có thể ập đến bất cứ lúc nào, và một ngày nào đó, chúng ta sẽ phải đối mặt với kẻ thù ngoài Stridergate.</t>
+          <t>Ở Học viện Startorch, ai cũng biết Bão Hư Không có thể ập đến bất cứ lúc nào, và một ngày nào đó, chúng ta sẽ phải đối mặt với kẻ thù ngoài Stridergate.</t>
         </is>
       </c>
     </row>
@@ -10817,7 +10817,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Chẳng có gì điên rồ đâu, chỉ là thử tăng sức mạnh cho vũ khí Resonance trong trận chiến cuối. Dodgem thêm hai viên Tacetite vào. Sức mạnh tăng gấp ba, phải không nào?</t>
+          <t>Chẳng có gì điên rồ đâu, chỉ là thử tăng sức mạnh cho vũ khí Cộng Hưởng trong trận chiến cuối. Ném thêm hai viên Tacetite vào. Sức mạnh tăng gấp ba, phải không nào?</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Nhận thức có thể xuyên qua Stridergate... Làm sao lại thế được? Một dạng Resonance mới chăng? Hừm. Một giả thuyết đáng để đào sâu...</t>
+          <t>Nhận thức có thể xuyên qua Stridergate... Làm sao lại thế được? Một dạng Cộng Hưởng mới chăng? Hừm. Một giả thuyết đáng để đào sâu...</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Giờ Void Storm đã tan, hệ sinh thái của Lahai-Roi sẽ dần hồi phục.</t>
+          <t>Giờ Bão Hư Không đã tan, hệ sinh thái của Lahai-Roi sẽ dần hồi phục.</t>
         </is>
       </c>
     </row>
@@ -11597,7 +11597,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>"Khi tỉnh lại, vật liệu Exoswarm đã bao phủ hết những chỗ tôi bị thương. Bác sĩ bảo có lẽ tôi đã Overclock Forte của mình. I think... chắc tôi đã dùng nó để hấp thụ thành phần của Exoswarm, chiếm lấy chức năng của nó. Đó là cách tôi sống sót được," Dhalifa kể!</t>
+          <t>"Khi tỉnh lại, vật liệu Exoswarm đã bao phủ hết những chỗ tôi bị thương. Bác sĩ bảo có lẽ tôi đã Overclock Forte của mình. Tôi nghĩ... chắc tôi đã dùng nó để hấp thụ thành phần của Exoswarm, chiếm lấy chức năng của nó. Đó là cách tôi sống sót được," Dhalifa kể!</t>
         </is>
       </c>
     </row>
@@ -12247,7 +12247,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>"Khi tỉnh lại, vật liệu Exoswarm đã bao phủ hết những chỗ tôi bị thương. Bác sĩ bảo có lẽ tôi đã Overclock Forte của mình. I think... chắc tôi đã dùng nó để hấp thụ thành phần của Exoswarm, chiếm lấy chức năng của nó. Đó là cách tôi sống sót được," Dhalifa kể!</t>
+          <t>"Khi tỉnh lại, vật liệu Exoswarm đã bao phủ hết những chỗ tôi bị thương. Bác sĩ bảo có lẽ tôi đã Overclock Forte của mình. Tôi nghĩ... chắc tôi đã dùng nó để hấp thụ thành phần của Exoswarm, chiếm lấy chức năng của nó. Đó là cách tôi sống sót được," Dhalifa kể!</t>
         </is>
       </c>
     </row>
@@ -12962,7 +12962,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Forte của tôi...</t>
+          <t>Forte của ta...</t>
         </is>
       </c>
     </row>
@@ -13027,7 +13027,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>"Khi tỉnh lại, vật liệu Exoswarm đã bao phủ hết những chỗ tôi bị thương. Bác sĩ bảo có lẽ tôi đã Overclock Forte của mình. I think... chắc tôi đã dùng nó để hấp thụ thành phần của Exoswarm, chiếm lấy chức năng của nó. Đó là cách tôi sống sót được," Dhalifa kể!</t>
+          <t>"Khi tỉnh lại, vật liệu Exoswarm đã bao phủ hết những chỗ tôi bị thương. Bác sĩ bảo có lẽ tôi đã Overclock Forte của mình. Tôi nghĩ... chắc tôi đã dùng nó để hấp thụ thành phần của Exoswarm, chiếm lấy chức năng của nó. Đó là cách tôi sống sót được," Dhalifa kể!</t>
         </is>
       </c>
     </row>
@@ -13352,7 +13352,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Giảng viên và học viên có đánh giá Năng lực Resonance Combat đạt tiêu chuẩn cần đến vị trí chiến đấu được phân công khi có thông báo.</t>
+          <t>Giảng viên và học viên có đánh giá Năng lực Cộng Hưởng Chiến Đấu đạt tiêu chuẩn cần đến vị trí chiến đấu được phân công khi có thông báo.</t>
         </is>
       </c>
     </row>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Một số Tacet Discord có ái lực với Void Storm sẽ thể hiện sự gia tăng về đặc tính chiến đấu.</t>
+          <t>Một số Tacet Discord có ái lực với Bão Hư Không sẽ thể hiện sự gia tăng về đặc tính chiến đấu.</t>
         </is>
       </c>
     </row>
@@ -13677,7 +13677,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>Một số bộ ngắt bị tác động nhẹ có thể tự phục hồi sau khi Void Storm tan đi. Những ảnh hưởng nghiêm trọng hơn sẽ cần phải thiết lập lại thủ công.</t>
+          <t>Một số bộ ngắt bị tác động nhẹ có thể tự phục hồi sau khi Bão Hư Không tan đi. Những ảnh hưởng nghiêm trọng hơn sẽ cần phải thiết lập lại thủ công.</t>
         </is>
       </c>
     </row>
@@ -13937,7 +13937,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Lệnh Combat Số 1: Chiếm thế chủ động và đè bẹp tinh thần kẻ địch bằng khí thế áp đảo!</t>
+          <t>Lệnh Chiến Đấu Số 1: Chiếm thế chủ động và đè bẹp tinh thần kẻ địch bằng khí thế áp đảo!</t>
         </is>
       </c>
     </row>
@@ -14587,7 +14587,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Calm nào, Shion. Đây là Zahira, bạn của ta. Và đó không phải lời nguyền đâu. Đó chỉ là Forte của cô ấy thôi.</t>
+          <t>Bình tĩnh nào, Shion. Đây là Zahira, bạn của ta. Và đó không phải lời nguyền đâu. Đó chỉ là Forte của cô ấy thôi.</t>
         </is>
       </c>
     </row>
@@ -16092,7 +16092,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Đây có phải... Forte của Hiyuki không?</t>
+          <t>Liệu đây có phải... Forte của Hiyuki?</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Và nghiên cứu của chúng ta, "phân tích dòng chảy Void Storm để xác định và thu hồi những thứ đã mất," chính là thứ có thể chữa lành những "vết thương băng giá" đó. Ta... cuối cùng cũng lại yêu công việc của mình!</t>
+          <t>Và nghiên cứu của chúng ta, "phân tích dòng chảy Bão Hư Không để xác định và thu hồi những thứ đã mất," chính là thứ có thể chữa lành những "vết thương băng giá" đó. Ta... cuối cùng cũng lại yêu công việc của mình!</t>
         </is>
       </c>
     </row>
@@ -16547,7 +16547,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Có kẻ đang lừa đảo ở Dimmr Plains, giả vờ tìm lại đồ bị mất do Void Storm. Nhưng thực chất chúng chỉ làm đồ giả rẻ tiền rồi bán cho những gia đình đang đau khổ!</t>
+          <t>Có kẻ đang lừa đảo ở Đồng Bằng Dimmr, giả vờ tìm lại đồ bị mất do Bão Hư Không. Nhưng thực chất chúng chỉ làm đồ giả rẻ tiền rồi bán cho những gia đình đang đau khổ!</t>
         </is>
       </c>
     </row>
@@ -16677,7 +16677,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Hắn muốn chúng ta dùng dữ liệu cũ của Void Storm và các bản khảo sát để khôi phục lại những đèn hiệu định vị mà hắn đã cài đặt trong các khu vực Void Storm. Mục tiêu là cải thiện thuật toán phục hồi của hắn.</t>
+          <t>Hắn muốn chúng ta dùng dữ liệu cũ của Bão Hư Không và các bản khảo sát để khôi phục lại những đèn hiệu định vị mà hắn đã cài đặt trong các khu vực Bão Hư Không. Mục tiêu là cải thiện thuật toán phục hồi của hắn.</t>
         </is>
       </c>
     </row>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Dù cậu nói vậy... Nhưng tớ cũng chẳng ngạc nhiên khi cậu nghi ngờ nó là giả. Trả tiền để lấy lại đồ thất lạc từ Void Storm – nghe quá đỗi viển vông. Chẳng trách họ không tìm thấy chiếc vòng cổ.</t>
+          <t>Dù cậu nói vậy... Nhưng tớ cũng chẳng ngạc nhiên khi cậu nghi ngờ nó là giả. Trả tiền để lấy lại đồ thất lạc từ Bão Hư Không – nghe quá đỗi viển vông. Chẳng trách họ không tìm thấy chiếc vòng cổ.</t>
         </is>
       </c>
     </row>
@@ -17976,7 +17976,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Analyzing điều kiện thời tiết. Độ ẩm không khí tăng nhanh và áp suất không khí giảm đột ngột.</t>
+          <t>Đang phân tích điều kiện thời tiết. Độ ẩm không khí tăng nhanh và áp suất không khí giảm đột ngột.</t>
         </is>
       </c>
     </row>
@@ -18041,7 +18041,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Đã phát hiện. Cá nhân phù hợp tiêu chí tìm kiếm. Analyzing danh tính mục tiêu: Nhà nghiên cứu của Bộ Đánh Giá Phòng Thí Nghiệm, Huaxu Academy. Gợi ý chủ đề trao đổi: "Xiaosheng" hoặc "Áp lực công việc."</t>
+          <t>Đã phát hiện. Cá nhân phù hợp tiêu chí tìm kiếm. Đang phân tích danh tính mục tiêu: Nhà nghiên cứu của Bộ Đánh Giá Phòng Thí Nghiệm, Học viện Huaxu. Gợi ý chủ đề trao đổi: "Xiaosheng" hoặc "Áp lực công việc."</t>
         </is>
       </c>
     </row>
@@ -18106,7 +18106,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Bíp. Bíp... Đã thu thập toàn bộ Echoes mục tiêu. Nhiệm vụ hoàn thành. Làm tốt lắm, {PlayerName}!</t>
+          <t>Bíp. Bíp... Đã thu thập toàn bộ Echo mục tiêu. Nhiệm vụ hoàn thành. Làm tốt lắm, {PlayerName}!</t>
         </is>
       </c>
     </row>
@@ -18236,7 +18236,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Forte của cậu?</t>
+          <t>Tần số của cậu à?</t>
         </is>
       </c>
     </row>
@@ -18366,7 +18366,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Rồi thì—"Sau bao năm rèn luyện, Echo cuối cùng cũng xuất hiện. Forte thức tỉnh." Hihi, đó là đoạn tớ thích nhất!</t>
+          <t>Rồi thì—"Sau bao năm rèn luyện, Tổ Tacet cuối cùng cũng xuất hiện. Forte thức tỉnh." Hihi, đó là đoạn tớ thích nhất!</t>
         </is>
       </c>
     </row>
@@ -19211,7 +19211,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>...Thật ra, người tôi nghĩ đến là hiện thân của lòng dũng cảm, sự kiên trì và khả năng lãnh đạo, luôn có những người đồng hành trung thành bên {Male=anh ấy;Female=cô ấy}, không bao giờ lùi bước dù đối mặt với kẻ thù mạnh mẽ đến đâu...</t>
+          <t>...Thật ra, người tôi nghĩ đến là hiện thân của lòng dũng cảm, sự kiên trì và khả năng lãnh đạo, luôn có những người đồng hành trung thành bên {Male=him;Female=her}, không bao giờ lùi bước dù đối mặt với kẻ thù mạnh mẽ đến đâu...</t>
         </is>
       </c>
     </row>
@@ -19276,7 +19276,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>...Thật ra, người tôi nghĩ đến là hiện thân của lòng dũng cảm, sự kiên trì và khả năng lãnh đạo, luôn có những người đồng hành trung thành bên {Male=anh ấy;Female=cô ấy}, không bao giờ lùi bước dù đối mặt với kẻ thù mạnh mẽ đến đâu...</t>
+          <t>...Thật ra, người tôi nghĩ đến là hiện thân của lòng dũng cảm, sự kiên trì và khả năng lãnh đạo, luôn có những người đồng hành trung thành bên {Male=him;Female=her}, không bao giờ lùi bước dù đối mặt với kẻ thù mạnh mẽ đến đâu...</t>
         </is>
       </c>
     </row>
@@ -19341,7 +19341,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>...Thật ra, người tôi nghĩ đến là hiện thân của lòng dũng cảm, sự kiên trì và khả năng lãnh đạo, luôn có những người đồng hành trung thành bên {Male=anh ấy;Female=cô ấy}, không bao giờ lùi bước dù đối mặt với kẻ thù mạnh mẽ đến đâu...</t>
+          <t>...Thật ra, người tôi nghĩ đến là hiện thân của lòng dũng cảm, sự kiên trì và khả năng lãnh đạo, luôn có những người đồng hành trung thành bên {Male=him;Female=her}, không bao giờ lùi bước dù đối mặt với kẻ thù mạnh mẽ đến đâu...</t>
         </is>
       </c>
     </row>
@@ -19471,7 +19471,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Phải... kích hoạt... Tacet Field... Waveworn...</t>
+          <t>Phải... kích hoạt... Tổ Tacet... Waveworn...</t>
         </is>
       </c>
     </row>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>...Không chính xác. Xác nhận mục tiêu.</t>
+          <t>...Sai rồi. Xác nhận mục tiêu.</t>
         </is>
       </c>
     </row>
@@ -20576,7 +20576,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Echo Tấn Công bằng 0 của cậu sẽ chẳng làm được gì đâu!</t>
+          <t>Echo ATK bằng 0 của cậu sẽ chẳng làm được gì đâu!</t>
         </is>
       </c>
     </row>
@@ -20641,7 +20641,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Echo Tấn Công bằng 0 của cậu sẽ chẳng làm được gì đâu!</t>
+          <t>Echo ATK bằng 0 của cậu sẽ chẳng làm được gì đâu!</t>
         </is>
       </c>
     </row>
@@ -20706,7 +20706,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Còn phải xem đã. Ta chỉ cần kích hoạt hiệu ứng đặc biệt của Echoes thôi. Giờ thì tất cả Echoes của ngươi đều bị suy yếu hết!</t>
+          <t>Còn phải xem đã. Tao chỉ cần kích hoạt hiệu ứng đặc biệt của Echo thôi. Giờ thì tất cả Echo của mày đều bị suy yếu hết!</t>
         </is>
       </c>
     </row>
@@ -21746,7 +21746,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Ngươi đến từ đâu, làm nghề gì, chẳng quan trọng. Nếu ngươi nghĩ tay súng của mình đủ cứng, thì đăng ký đi!</t>
+          <t>Mày đến từ đâu, làm nghề gì, chẳng quan trọng. Nếu mày nghĩ tay súng của mình đủ cứng, thì đăng ký đi!</t>
         </is>
       </c>
     </row>
@@ -22656,7 +22656,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Ừ, ngà dài, vuốt sắc, lại còn dấu vết của năng lượng Resonance...</t>
+          <t>Ừ, ngà dài, vuốt sắc, lại còn dấu vết của năng lượng Cộng Hưởng...</t>
         </is>
       </c>
     </row>
@@ -23176,7 +23176,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>(Dollmaker đang nghiên cứu sâu về Forte của hắn, cố gắng tạo ra một con rối nhất định.)</t>
+          <t>(Thợ làm búp bê đang nghiên cứu sâu về Forte của hắn, cố gắng tạo ra một con rối nhất định.)</t>
         </is>
       </c>
     </row>
@@ -23241,7 +23241,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Không có vết thương nào trên người Yuanyuan cả. Người phụ nữ đó cũng không điều khiển cô ấy qua Khả Năng Resonance.</t>
+          <t>Không có vết thương nào trên người Yuanyuan cả. Người phụ nữ đó cũng không điều khiển cô ấy qua Khả Năng Cộng Hưởng.</t>
         </is>
       </c>
     </row>
@@ -24151,7 +24151,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Pistols là loại súng cầm tay nhỏ gọn sử dụng Resonance Energy để tạo ra những viên đạn có sức công phá mạnh mẽ.</t>
+          <t>Súng là loại súng cầm tay nhỏ gọn sử dụng Resonance Energy để tạo ra những viên đạn có sức công phá mạnh mẽ.</t>
         </is>
       </c>
     </row>
@@ -24346,7 +24346,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>Cần vũ khí để hạ gục những Tacet Discord cứng đầu à? Vậy thì Broadblade là lựa chọn của cậu. Nó gây rất nhiều sát thương đấy.</t>
+          <t>Cần vũ khí để hạ gục những Tacet Discord cứng đầu à? Vậy thì Đại kiếm là lựa chọn của cậu. Nó gây rất nhiều sát thương đấy.</t>
         </is>
       </c>
     </row>
@@ -26621,7 +26621,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Sắp tới nơi rồi! Đúng chỗ hẹn gặp Baizhi đấy! Cô ấy chính là Resonator mà ta vẫn kể. Baizhi có thể chữa thương bằng Resonance Ability, và chúng ta đã tìm thấy ngươi cùng cô ấy dưới vực sâu kia.</t>
+          <t>Sắp tới nơi rồi! Đúng chỗ hẹn gặp Baizhi đấy! Cô ấy chính là Resonator mà tao vẫn kể. Baizhi có thể chữa thương bằng Khả Năng Cộng Hưởng, và chúng ta đã tìm thấy mày cùng cô ấy dưới vực sâu kia.</t>
         </is>
       </c>
     </row>
@@ -26686,7 +26686,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Thấy chưa? Có một Đèn Tín Hiệu Resonance ở đằng kia.</t>
+          <t>Thấy chưa? Có một Đèn Tín Hiệu Cộng Hưởng ở đằng kia.</t>
         </is>
       </c>
     </row>
@@ -26751,7 +26751,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Jinzhou là nơi an toàn nhất quanh đây. Mạng lưới Resonance bao phủ toàn thành phố. Ngoài ra, chúng ta còn có lá chắn bảo vệ và công sự vững chắc!</t>
+          <t>Jinzhou là nơi an toàn nhất quanh đây. Mạng lưới Cộng Hưởng bao phủ toàn thành phố. Ngoài ra, chúng ta còn có lá chắn bảo vệ và công sự vững chắc!</t>
         </is>
       </c>
     </row>
@@ -26816,7 +26816,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>Sẽ không lâu nữa đâu, khi Dư Âm tan biến và Etheric Seaic biến mất. Khi đó, tín hiệu Đèn Hiệu Resonance sẽ trở lại thôi.</t>
+          <t>Sẽ không lâu nữa đâu, khi Dư Âm tan biến và Biển Etheric biến mất. Khi đó, tín hiệu Đèn Hiệu Cộng Hưởng sẽ trở lại thôi.</t>
         </is>
       </c>
     </row>
@@ -26881,7 +26881,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Ta chưa từng thấy Resonance Ability nào như thế này bao giờ. Cậu còn chiêu trò gì khác không? Chẳng hạn như nuốt chửng nguyên một Discord? Hay nướng sống mấy con Echoes?</t>
+          <t>Ta chưa từng thấy Khả Năng Cộng Hưởng nào như thế này bao giờ. Cậu còn chiêu trò gì khác không? Chẳng hạn như nuốt chửng nguyên một Tacet Discord? Hay nướng sống mấy con Echo?</t>
         </is>
       </c>
     </row>
@@ -26946,7 +26946,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Đó không phải Resonance Ability của tôi.</t>
+          <t>Đó không phải là Khả Năng Cộng Hưởng của ta.</t>
         </is>
       </c>
     </row>
@@ -27011,7 +27011,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Đó không phải Resonance Ability của cậu à?</t>
+          <t>Khả năng Cộng Hưởng của cậu phải không?</t>
         </is>
       </c>
     </row>
@@ -27076,7 +27076,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Hay là do tác dụng phụ sau khi chiến đấu với Discord đó? Baizhi, chúng ta có thể đưa Rover đến Khoa Y Học Resonance của Huaxu Academy để kiểm tra không...</t>
+          <t>Hay là do tác dụng phụ sau khi chiến đấu với Tacet Discord đó? Baizhi, chúng ta có thể đưa Rover đến Khoa Y Học Cộng Hưởng của Học viện Huaxu để kiểm tra không...</t>
         </is>
       </c>
     </row>
@@ -27141,7 +27141,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Ngoài ra, chúng ta có những &lt;color=Highlight&gt;Resonators&lt;/color&gt; có thể phát hiện sự hình thành của Tacet Field gần đó, như Yangyang vừa làm. Cô ấy có thể đọc được đủ loại thông tin từ những Luồng Gió—đó là Resonance Ability của cô ấy.</t>
+          <t>Ngoài ra, chúng ta có những &lt;color=Highlight&gt;Resonator&lt;/color&gt; có thể phát hiện sự hình thành của Tổ Tacet gần đó, như Yangyang vừa làm. Cô ấy có thể đọc được đủ loại thông tin từ những Luồng Gió—đó là Khả Năng Cộng Hưởng của cô ấy.</t>
         </is>
       </c>
     </row>
@@ -27206,7 +27206,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Cô ấy còn được gọi là "Thiếu Nữ Dragon", vì mối liên kết Resonance với Sentinel của chúng ta, "Jué", người hiện thân dưới hình dáng một &lt;ano=Dragon&gt;Dragon&lt;/ano&gt;.</t>
+          <t>Cô ấy còn được gọi là "Thiếu Nữ Rồng", vì mối liên kết Cộng Hưởng với Sentinel của chúng ta, "Jué", người hiện thân dưới hình dáng một &lt;ano=Dragon&gt;Rồng&lt;/ano&gt;.</t>
         </is>
       </c>
     </row>
@@ -27271,7 +27271,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Giờ cậu đã được cấp quyền ra vào không giới hạn tất cả các khu vực ở Jinzhou. Ta đã gửi ID Terminal của cậu đến mọi trạm kiểm soát và Đèn Cảm Ứng. Cậu chỉ cần xuất trình ID Terminal hoặc kích hoạt Đèn Cảm Ứng bằng thiết bị của mình là có thể qua cửa.</t>
+          <t>Giờ cậu đã được cấp quyền ra vào không giới hạn tất cả các khu vực ở Jinzhou. Ta đã gửi ID Thiết bị đầu cuối của cậu đến mọi trạm kiểm soát và Đèn Cảm Ứng. Cậu chỉ cần xuất trình ID Thiết bị đầu cuối hoặc kích hoạt Đèn Cảm Ứng bằng thiết bị của mình là có thể qua cửa.</t>
         </is>
       </c>
     </row>
@@ -27336,7 +27336,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>Những cái nhỏ hơn mà chúng ta gặp trước đó là Resonance Beacon.</t>
+          <t>Những cái nhỏ hơn mà chúng ta gặp trước đó là Đèn Cộng Hưởng.</t>
         </is>
       </c>
     </row>
@@ -27401,7 +27401,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>What do you think, Rover? Có vội lấy lại ký ức không?</t>
+          <t>Cậu nghĩ sao, Rover? Có vội lấy lại ký ức không?</t>
         </is>
       </c>
     </row>
@@ -32666,7 +32666,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Cảm ơn so much. Ta đang cố thuyết phục ông ấy về nhà điều trị đúng cách, hy vọng ông ấy sẽ sớm bình phục.</t>
+          <t>Cảm ơn cậu rất nhiều. Ta đang cố thuyết phục ông ấy về nhà điều trị đúng cách, hy vọng ông ấy sẽ sớm bình phục.</t>
         </is>
       </c>
     </row>
